--- a/tools/importer/reports/import-product-landing.report.xlsx
+++ b/tools/importer/reports/import-product-landing.report.xlsx
@@ -46,7 +46,7 @@
     <t>product-landing</t>
   </si>
   <si>
-    <t>2026-07-03T11:48:51.636Z</t>
+    <t>2026-07-03T15:19:51.475Z</t>
   </si>
   <si>
     <t>Current mortgage rates | Wells Fargo</t>
